--- a/data/trans_dic/IP38F_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP38F_2023-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto que aporta más ingresos al hogar que ha trabajado anteriormente</t>
+          <t>Adulto que aporta más ingresos al hogar que ha trabajado anteriormente (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -576,19 +577,19 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 100,0</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -621,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,57; 100,0</t>
+          <t>35,44; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,23; 100,0</t>
+          <t>19,7; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45,36; 92,22</t>
+          <t>44,95; 92,66</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52,3; 100,0</t>
+          <t>48,74; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>70,91; 100,0</t>
+          <t>78,99; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74,34; 97,59</t>
+          <t>71,26; 97,39</t>
         </is>
       </c>
     </row>
@@ -771,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>73,58; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>76,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86,51; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -821,24 +822,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>88,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>91,36; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>94,97; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>56,87; 100,0</t>
+          <t>60,18; 100,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>79,25; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74,62; 100,0</t>
+          <t>71,18; 100,0</t>
         </is>
       </c>
     </row>
@@ -921,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>69,43; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>79,25; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>86,51; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -971,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>79,72; 95,55</t>
+          <t>78,94; 95,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>86,56; 99,12</t>
+          <t>87,44; 99,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>87,33; 96,29</t>
+          <t>86,76; 96,7</t>
         </is>
       </c>
     </row>
@@ -1007,4 +1008,750 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adulto que aporta más ingresos al hogar que ha trabajado anteriormente (tasa de respuesta: 99,23%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1288</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2737</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4189</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3828</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8017</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1920; 5419</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1031; 5236</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4789; 9873</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>5935</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8116</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14051</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>3500; 7181</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6712; 8497</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11172; 15269</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1683</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1683</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2128</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2128</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3067</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4012</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7079</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>9354</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>12170</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>21524</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>8386</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>6477</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>14863</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>5521; 9174</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>11141; 15651</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>4267</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>6636</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>10903</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>37450</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>42688</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>80137</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>33060; 40102</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>38889; 44090</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>74918; 83506</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP38F_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP38F_2023-Provincia-trans_dic.xlsx
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,44; 100,0</t>
+          <t>35,51; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,7; 100,0</t>
+          <t>21,24; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44,95; 92,66</t>
+          <t>46,1; 92,2</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>48,74; 100,0</t>
+          <t>47,4; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>78,99; 100,0</t>
+          <t>76,83; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>71,26; 97,39</t>
+          <t>71,67; 97,59</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>60,18; 100,0</t>
+          <t>56,93; 100,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71,18; 100,0</t>
+          <t>75,84; 100,0</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>78,94; 95,76</t>
+          <t>79,97; 95,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>87,44; 99,13</t>
+          <t>86,39; 99,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>86,76; 96,7</t>
+          <t>87,28; 96,68</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1920; 5419</t>
+          <t>1924; 5419</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1031; 5236</t>
+          <t>1112; 5236</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4789; 9873</t>
+          <t>4912; 9824</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3500; 7181</t>
+          <t>3404; 7181</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6712; 8497</t>
+          <t>6529; 8497</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11172; 15269</t>
+          <t>11237; 15299</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5521; 9174</t>
+          <t>5223; 9174</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11141; 15651</t>
+          <t>11870; 15651</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>33060; 40102</t>
+          <t>33489; 40057</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>38889; 44090</t>
+          <t>38422; 44091</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>74918; 83506</t>
+          <t>75373; 83490</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP38F_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP38F_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>71,43%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>18,95; 100,0</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,93%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,51; 100,0</t>
+          <t>16,79; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,24; 100,0</t>
+          <t>36,49; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46,1; 92,2</t>
+          <t>44,82; 92,89</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,24%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>47,4; 100,0</t>
+          <t>73,07; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>76,83; 100,0</t>
+          <t>49,52; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>71,67; 97,59</t>
+          <t>73,32; 97,81</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>83,29%</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>93,55%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>56,93; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>45,81; 100,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>75,84; 100,0</t>
+          <t>67,99; 100,0</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>79,97; 95,65</t>
+          <t>86,01; 99,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>86,39; 99,13</t>
+          <t>79,35; 95,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>87,28; 96,68</t>
+          <t>86,83; 96,34</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>468</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>1668</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1288</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 1135</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2737</t>
+          <t>442; 2335</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8017</t>
+          <t>7808</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1924; 5419</t>
+          <t>817; 4865</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1112; 5236</t>
+          <t>1977; 5418</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4912; 9824</t>
+          <t>4609; 9552</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>5582</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14051</t>
+          <t>12857</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3404; 7181</t>
+          <t>5546; 7590</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6529; 8497</t>
+          <t>3376; 6818</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11237; 15299</t>
+          <t>10564; 14092</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1683</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1683</t>
+          <t>1790</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2128</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2149</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2128</t>
+          <t>0; 2149</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>7323</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>9354</t>
+          <t>10690</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>12170</t>
+          <t>9525</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21524</t>
+          <t>20215</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>8386</t>
+          <t>6561</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>5901</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14863</t>
+          <t>12462</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5223; 9174</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3097; 6761</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11870; 15651</t>
+          <t>9058; 13322</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>4671</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10903</t>
+          <t>11619</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>54</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>37450</t>
+          <t>40269</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>42688</t>
+          <t>35473</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>80137</t>
+          <t>75743</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>33489; 40057</t>
+          <t>36010; 41558</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>38422; 44091</t>
+          <t>31567; 37926</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>75373; 83490</t>
+          <t>70902; 78667</t>
         </is>
       </c>
     </row>
